--- a/doc/talks/2026-paleorient/out/membership_table.xlsx
+++ b/doc/talks/2026-paleorient/out/membership_table.xlsx
@@ -1234,7 +1234,7 @@
         <v>69</v>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
